--- a/Купол Энергетики/Сonsumption plan Data_frame_1.xlsx
+++ b/Купол Энергетики/Сonsumption plan Data_frame_1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -468,21 +468,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L102"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="6" width="8.88671875" style="6"/>
-    <col min="7" max="7" width="12.21875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="23.44140625" style="6" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" style="6" customWidth="1"/>
-    <col min="11" max="11" width="17.6640625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" style="6" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="3" width="8.90625" style="1"/>
+    <col min="4" max="6" width="8.90625" style="6"/>
+    <col min="7" max="7" width="12.1796875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="23.453125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" style="6" customWidth="1"/>
+    <col min="11" max="11" width="17.6328125" style="6" customWidth="1"/>
+    <col min="12" max="12" width="16.6328125" style="6" customWidth="1"/>
+    <col min="13" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>14</v>
       </c>
@@ -504,7 +504,7 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
     </row>
-    <row r="2" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="10"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -540,7 +540,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <f>ROW()-2</f>
         <v>1</v>
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D3" s="5">
         <v>30</v>
@@ -571,7 +571,7 @@
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <f t="shared" ref="A4:A67" si="0">ROW()-2</f>
         <v>2</v>
@@ -580,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D4" s="5">
         <v>24</v>
@@ -602,7 +602,7 @@
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -611,7 +611,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5">
         <v>39</v>
@@ -633,7 +633,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D6" s="5">
         <v>34</v>
@@ -664,7 +664,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5">
         <v>39</v>
@@ -682,7 +682,7 @@
         <v>51</v>
       </c>
       <c r="F7" s="5">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="G7" s="5">
         <v>37</v>
@@ -695,7 +695,7 @@
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D8" s="5">
         <v>42</v>
@@ -726,7 +726,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -735,7 +735,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D9" s="5">
         <v>32</v>
@@ -757,7 +757,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D10" s="5">
         <v>49</v>
@@ -788,7 +788,7 @@
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D11" s="5">
         <v>46</v>
@@ -819,7 +819,7 @@
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="D12" s="5">
         <v>58</v>
@@ -850,7 +850,7 @@
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D13" s="5">
         <v>59</v>
@@ -881,7 +881,7 @@
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -890,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="3">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D14" s="5">
         <v>47</v>
@@ -912,7 +912,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -921,7 +921,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="3">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D15" s="5">
         <v>49</v>
@@ -943,7 +943,7 @@
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -952,7 +952,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="3">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D16" s="5">
         <v>57</v>
@@ -974,7 +974,7 @@
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -983,7 +983,7 @@
         <v>26</v>
       </c>
       <c r="C17" s="3">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D17" s="5">
         <v>52</v>
@@ -1005,7 +1005,7 @@
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1014,7 +1014,7 @@
         <v>26</v>
       </c>
       <c r="C18" s="3">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D18" s="5">
         <v>66</v>
@@ -1036,7 +1036,7 @@
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1045,7 +1045,7 @@
         <v>35</v>
       </c>
       <c r="C19" s="3">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D19" s="5">
         <v>65</v>
@@ -1067,7 +1067,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1076,7 +1076,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="3">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="D20" s="5">
         <v>58</v>
@@ -1098,7 +1098,7 @@
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <f>ROW()-2</f>
         <v>19</v>
@@ -1107,7 +1107,7 @@
         <v>47</v>
       </c>
       <c r="C21" s="3">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D21" s="5">
         <v>70</v>
@@ -1129,7 +1129,7 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1138,7 +1138,7 @@
         <v>45</v>
       </c>
       <c r="C22" s="3">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D22" s="5">
         <v>72</v>
@@ -1160,7 +1160,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1169,7 +1169,7 @@
         <v>48</v>
       </c>
       <c r="C23" s="3">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="D23" s="5">
         <v>79</v>
@@ -1191,7 +1191,7 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1200,7 +1200,7 @@
         <v>43</v>
       </c>
       <c r="C24" s="3">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D24" s="5">
         <v>75</v>
@@ -1222,7 +1222,7 @@
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1231,7 +1231,7 @@
         <v>44</v>
       </c>
       <c r="C25" s="3">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D25" s="5">
         <v>69</v>
@@ -1253,7 +1253,7 @@
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1262,7 +1262,7 @@
         <v>48</v>
       </c>
       <c r="C26" s="3">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="D26" s="5">
         <v>82</v>
@@ -1284,7 +1284,7 @@
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1293,7 +1293,7 @@
         <v>52</v>
       </c>
       <c r="C27" s="3">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="D27" s="5">
         <v>74</v>
@@ -1315,16 +1315,16 @@
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C28" s="3">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="D28" s="7">
         <v>87</v>
@@ -1346,16 +1346,16 @@
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C29" s="3">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D29" s="7">
         <v>78</v>
@@ -1377,16 +1377,16 @@
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C30" s="3">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="D30" s="7">
         <v>74</v>
@@ -1408,16 +1408,16 @@
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="3">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="D31" s="7">
         <v>85</v>
@@ -1439,7 +1439,7 @@
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1448,7 +1448,7 @@
         <v>66</v>
       </c>
       <c r="C32" s="3">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D32" s="7">
         <v>96</v>
@@ -1470,7 +1470,7 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1479,7 +1479,7 @@
         <v>58</v>
       </c>
       <c r="C33" s="3">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="D33" s="7">
         <v>93</v>
@@ -1501,7 +1501,7 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -1510,7 +1510,7 @@
         <v>57</v>
       </c>
       <c r="C34" s="3">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="D34" s="7">
         <v>85</v>
@@ -1532,7 +1532,7 @@
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -1541,7 +1541,7 @@
         <v>56</v>
       </c>
       <c r="C35" s="3">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="D35" s="7">
         <v>83</v>
@@ -1563,7 +1563,7 @@
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -1572,7 +1572,7 @@
         <v>53</v>
       </c>
       <c r="C36" s="3">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="D36" s="7">
         <v>91</v>
@@ -1594,7 +1594,7 @@
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -1603,7 +1603,7 @@
         <v>43</v>
       </c>
       <c r="C37" s="3">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="D37" s="7">
         <v>82</v>
@@ -1625,7 +1625,7 @@
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -1634,7 +1634,7 @@
         <v>45</v>
       </c>
       <c r="C38" s="3">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="D38" s="7">
         <v>92</v>
@@ -1656,7 +1656,7 @@
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -1665,7 +1665,7 @@
         <v>46</v>
       </c>
       <c r="C39" s="3">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D39" s="7">
         <v>84</v>
@@ -1687,7 +1687,7 @@
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -1696,7 +1696,7 @@
         <v>37</v>
       </c>
       <c r="C40" s="3">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="D40" s="7">
         <v>72</v>
@@ -1718,7 +1718,7 @@
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -1727,7 +1727,7 @@
         <v>27</v>
       </c>
       <c r="C41" s="3">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D41" s="7">
         <v>71</v>
@@ -1749,7 +1749,7 @@
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -1758,7 +1758,7 @@
         <v>21</v>
       </c>
       <c r="C42" s="3">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D42" s="7">
         <v>76</v>
@@ -1780,7 +1780,7 @@
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -1789,7 +1789,7 @@
         <v>23</v>
       </c>
       <c r="C43" s="3">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D43" s="7">
         <v>76</v>
@@ -1811,7 +1811,7 @@
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -1820,7 +1820,7 @@
         <v>27</v>
       </c>
       <c r="C44" s="3">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="D44" s="7">
         <v>81</v>
@@ -1842,7 +1842,7 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -1851,7 +1851,7 @@
         <v>27</v>
       </c>
       <c r="C45" s="3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D45" s="7">
         <v>64</v>
@@ -1873,7 +1873,7 @@
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -1882,7 +1882,7 @@
         <v>29</v>
       </c>
       <c r="C46" s="3">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="D46" s="7">
         <v>74</v>
@@ -1904,7 +1904,7 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -1935,7 +1935,7 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -1944,7 +1944,7 @@
         <v>31</v>
       </c>
       <c r="C48" s="3">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D48" s="7">
         <v>65</v>
@@ -1966,7 +1966,7 @@
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -1975,7 +1975,7 @@
         <v>25</v>
       </c>
       <c r="C49" s="3">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D49" s="7">
         <v>61</v>
@@ -1997,7 +1997,7 @@
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -2028,7 +2028,7 @@
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -2059,7 +2059,7 @@
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -2090,7 +2090,7 @@
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -2121,7 +2121,7 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -2152,7 +2152,7 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -2183,7 +2183,7 @@
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -2214,7 +2214,7 @@
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -2245,7 +2245,7 @@
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -2276,7 +2276,7 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -2307,7 +2307,7 @@
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -2338,7 +2338,7 @@
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -2369,7 +2369,7 @@
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -2400,7 +2400,7 @@
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -2431,7 +2431,7 @@
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -2462,7 +2462,7 @@
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -2493,7 +2493,7 @@
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -2524,7 +2524,7 @@
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -2555,7 +2555,7 @@
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
         <f t="shared" ref="A68:A102" si="1">ROW()-2</f>
         <v>66</v>
@@ -2586,7 +2586,7 @@
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
         <f t="shared" si="1"/>
         <v>67</v>
@@ -2617,7 +2617,7 @@
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -2648,7 +2648,7 @@
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -2679,7 +2679,7 @@
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -2710,7 +2710,7 @@
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -2741,7 +2741,7 @@
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -2772,7 +2772,7 @@
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -2803,7 +2803,7 @@
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -2834,7 +2834,7 @@
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -2865,13 +2865,13 @@
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="B78" s="3">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C78" s="3">
         <v>7</v>
@@ -2896,13 +2896,13 @@
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="B79" s="3">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C79" s="3">
         <v>2</v>
@@ -2927,13 +2927,13 @@
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="B80" s="3">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="C80" s="3">
         <v>2</v>
@@ -2958,13 +2958,13 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="B81" s="3">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C81" s="3">
         <v>1</v>
@@ -2989,13 +2989,13 @@
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="B82" s="3">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C82" s="3">
         <v>2</v>
@@ -3020,13 +3020,13 @@
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
       <c r="B83" s="3">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="C83" s="3">
         <v>0</v>
@@ -3051,13 +3051,13 @@
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="B84" s="3">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="C84" s="3">
         <v>8</v>
@@ -3082,13 +3082,13 @@
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
       <c r="B85" s="3">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C85" s="3">
         <v>1</v>
@@ -3113,13 +3113,13 @@
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="B86" s="3">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C86" s="3">
         <v>0</v>
@@ -3144,13 +3144,13 @@
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="B87" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C87" s="3">
         <v>3</v>
@@ -3175,13 +3175,13 @@
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="B88" s="3">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="C88" s="3">
         <v>2</v>
@@ -3206,13 +3206,13 @@
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
       <c r="B89" s="3">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="C89" s="3">
         <v>0</v>
@@ -3237,13 +3237,13 @@
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="B90" s="3">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="C90" s="3">
         <v>3</v>
@@ -3268,13 +3268,13 @@
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="B91" s="3">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C91" s="3">
         <v>4</v>
@@ -3299,13 +3299,13 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="3">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B92" s="3">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C92" s="3">
         <v>3</v>
@@ -3330,13 +3330,13 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
       <c r="B93" s="3">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="C93" s="3">
         <v>0</v>
@@ -3361,13 +3361,13 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="B94" s="3">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C94" s="3">
         <v>2</v>
@@ -3392,13 +3392,13 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
       <c r="B95" s="3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C95" s="3">
         <v>0</v>
@@ -3423,7 +3423,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -3454,7 +3454,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -3485,7 +3485,7 @@
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -3516,7 +3516,7 @@
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -3547,7 +3547,7 @@
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -3578,7 +3578,7 @@
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -3609,7 +3609,7 @@
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -3641,7 +3641,7 @@
       <c r="L102" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="RUhbQfLl9m8J6vC7vOMpTJMBQXGLxaLirPTToJysSHGH70X+9loAzwhjo9tBog62mwA9mALOhBNq2pjNfgCNBg==" saltValue="3BRgYGgoDgKAltgK1mzwzw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="CC71" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="4">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:G1"/>
